--- a/docs/source data 2.xlsx
+++ b/docs/source data 2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louis\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\louis\Desktop\network-packet-classification\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37563E30-97FD-430E-AA11-EC84B20C0BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECECF19A-1350-46D3-8B6B-918B2F28DC3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="64">
   <si>
     <t>1us: ^(-3) ms</t>
   </si>
@@ -196,12 +196,39 @@
     <t>using TM-ONLINE</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
+  <si>
+    <t>CutTSS-V3.1</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Build (s)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Memory (KB)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>CutSplit</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Search-avg (us)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Update-avg (us)</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>RVH</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -301,6 +328,11 @@
       <name val="細明體"/>
       <family val="3"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Liberation Sans1"/>
     </font>
   </fonts>
   <fills count="9">
@@ -436,8 +468,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1377,6 +1412,127 @@
           </c:extLst>
         </c:ser>
         <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tmp!$I$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>KickTree</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="AECF00"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>tmp!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>acl1_100k</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>acl2_100k</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>acl3_100k</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>acl4_100k</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>acl5_100k</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>fw1_100k</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>fw2_100k</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>fw3_100k</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>fw4_100k</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>fw5_100k</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>ipc1_100k</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>ipc2_100k</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>tmp!$I$4:$I$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>1.9177999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.75488</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.86407999999999996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.95157999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.37294</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3.1215600000000001</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.3546199999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7.8689200000000001</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>8.7195300000000007</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3.0695999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.85531999999999997</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.0165999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-5CC1-4EEE-B8A1-20FB54D71AA7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="8"/>
           <c:order val="8"/>
           <c:tx>
@@ -2874,6 +3030,132 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="21"/>
+          <c:order val="21"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tmp!$W$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RVH</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>tmp!$W$4:$W$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.13800000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13880999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.13868</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13877</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.14387</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.13553999999999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.13649</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.14011000000000001</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.13849</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.13735</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-344A-4BFB-A81C-1AF55DDB89FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="22"/>
+          <c:order val="22"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tmp!$X$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CutSplit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>tmp!$X$4:$X$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.171043</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.31703999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17954999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.16584599999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.190941</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.19268199999999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.156449</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.19232199999999999</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.245118</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.18124699999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.179868</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.197049</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-344A-4BFB-A81C-1AF55DDB89FA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -2885,148 +3167,7 @@
         <c:gapWidth val="150"/>
         <c:axId val="1666154287"/>
         <c:axId val="1667130559"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredBarSeries>
-              <c15:ser>
-                <c:idx val="7"/>
-                <c:order val="7"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>tmp!$I$3</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>KickTree</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:solidFill>
-                    <a:srgbClr val="AECF00"/>
-                  </a:solidFill>
-                  <a:ln>
-                    <a:noFill/>
-                  </a:ln>
-                </c:spPr>
-                <c:invertIfNegative val="0"/>
-                <c:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>tmp!$A$4:$A$15</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="12"/>
-                      <c:pt idx="0">
-                        <c:v>acl1_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>acl2_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>acl3_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>acl4_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>acl5_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>fw1_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>fw2_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>fw3_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>fw4_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>fw5_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>ipc1_100k</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>ipc2_100k</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>tmp!$I$4:$I$15</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="12"/>
-                      <c:pt idx="0">
-                        <c:v>1.9177999999999999</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>7.75488</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>0.86407999999999996</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>0.95157999999999998</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>1.37294</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>3.1215600000000001</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>1.3546199999999999</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>7.8689200000000001</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>8.7195300000000007</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>3.0695999999999999</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>0.85531999999999997</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>2.0165999999999999</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000007-5CC1-4EEE-B8A1-20FB54D71AA7}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredBarSeries>
-          </c:ext>
-        </c:extLst>
+        <c:extLst/>
       </c:barChart>
       <c:valAx>
         <c:axId val="1667130559"/>
@@ -5710,6 +5851,102 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000014-2A0A-4864-B027-E49F187F90AA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="21"/>
+          <c:order val="21"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tmp!$W$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RVH</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>tmp!$W$18:$W$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AC24-499B-BC84-988610ED0092}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="22"/>
+          <c:order val="22"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tmp!$X$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CutSplit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>tmp!$X$18:$X$29</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>524.42578100000003</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>632.83886700000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1063.3701169999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1096.1835940000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>503.69726600000001</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>510.13574199999999</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>199.52246099999999</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>253.570312</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>39516.113280999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>372.328125</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1126.993164</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>208.92089799999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AC24-499B-BC84-988610ED0092}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8230,6 +8467,66 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:ser>
+          <c:idx val="21"/>
+          <c:order val="21"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tmp!$W$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RVH</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>tmp!$W$32:$W$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-54EB-48A9-B8E6-6D7CF1D95259}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="22"/>
+          <c:order val="22"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tmp!$X$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CutSplit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>tmp!$X$32:$X$43</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-54EB-48A9-B8E6-6D7CF1D95259}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -10960,6 +11257,102 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000014-6332-4BD9-965E-273C6108D466}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="21"/>
+          <c:order val="21"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tmp!$W$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>RVH</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>tmp!$W$46:$W$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6179-4724-B054-378B2F82DBD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="22"/>
+          <c:order val="22"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>tmp!$X$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CutSplit</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>tmp!$X$46:$X$57</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>0.26600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.378</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.189</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.29599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.46800000000000003</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.184</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.46700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.45100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.17599999999999999</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.20100000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6179-4724-B054-378B2F82DBD3}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -22356,7 +22749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE1818D2-3FAD-40A7-AD2E-4D4E0AB600A3}">
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="9" width="12.796875" customWidth="1"/>
@@ -22366,8 +22759,8 @@
     <col min="18" max="18" width="11.296875" customWidth="1"/>
     <col min="19" max="19" width="10.8984375" customWidth="1"/>
     <col min="20" max="20" width="9.3984375" customWidth="1"/>
-    <col min="21" max="23" width="12.796875" customWidth="1"/>
-    <col min="24" max="24" width="15.19921875" customWidth="1"/>
+    <col min="21" max="22" width="12.796875" customWidth="1"/>
+    <col min="23" max="23" width="14.19921875" customWidth="1"/>
     <col min="25" max="25" width="15.296875" customWidth="1"/>
     <col min="26" max="26" width="16.59765625" customWidth="1"/>
     <col min="27" max="27" width="16" customWidth="1"/>
@@ -22375,7 +22768,7 @@
     <col min="29" max="29" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -22386,12 +22779,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:24">
       <c r="K2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -22458,8 +22851,14 @@
       <c r="V3" t="s">
         <v>25</v>
       </c>
+      <c r="W3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="X3" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -22523,8 +22922,14 @@
       <c r="U4">
         <v>0.10299999999999999</v>
       </c>
+      <c r="W4">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="X4">
+        <v>0.171043</v>
+      </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:24">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -22588,8 +22993,14 @@
       <c r="U5">
         <v>0.91500000000000004</v>
       </c>
+      <c r="W5">
+        <v>0.13880999999999999</v>
+      </c>
+      <c r="X5">
+        <v>0.31703999999999999</v>
+      </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -22653,8 +23064,14 @@
       <c r="U6">
         <v>0.111</v>
       </c>
+      <c r="W6">
+        <v>0.13868</v>
+      </c>
+      <c r="X6">
+        <v>0.17954999999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -22718,8 +23135,14 @@
       <c r="U7">
         <v>0.184</v>
       </c>
+      <c r="W7">
+        <v>0.13877</v>
+      </c>
+      <c r="X7">
+        <v>0.16584599999999999</v>
+      </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -22783,8 +23206,11 @@
       <c r="U8">
         <v>0.17699999999999999</v>
       </c>
+      <c r="X8">
+        <v>0.190941</v>
+      </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -22848,8 +23274,14 @@
       <c r="U9">
         <v>0.21</v>
       </c>
+      <c r="W9">
+        <v>0.14387</v>
+      </c>
+      <c r="X9">
+        <v>0.19268199999999999</v>
+      </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -22913,8 +23345,14 @@
       <c r="U10">
         <v>0.16300000000000001</v>
       </c>
+      <c r="W10">
+        <v>0.13553999999999999</v>
+      </c>
+      <c r="X10">
+        <v>0.156449</v>
+      </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -22978,8 +23416,14 @@
       <c r="U11">
         <v>0.183</v>
       </c>
+      <c r="W11">
+        <v>0.13649</v>
+      </c>
+      <c r="X11">
+        <v>0.19232199999999999</v>
+      </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -23043,8 +23487,14 @@
       <c r="U12">
         <v>0.222</v>
       </c>
+      <c r="W12">
+        <v>0.14011000000000001</v>
+      </c>
+      <c r="X12">
+        <v>0.245118</v>
+      </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -23108,8 +23558,14 @@
       <c r="U13">
         <v>0.17</v>
       </c>
+      <c r="W13">
+        <v>0.13849</v>
+      </c>
+      <c r="X13">
+        <v>0.18124699999999999</v>
+      </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -23173,8 +23629,14 @@
       <c r="U14">
         <v>0.154</v>
       </c>
+      <c r="W14">
+        <v>0.13735</v>
+      </c>
+      <c r="X14">
+        <v>0.179868</v>
+      </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -23238,8 +23700,11 @@
       <c r="U15">
         <v>0.12</v>
       </c>
+      <c r="X15">
+        <v>0.197049</v>
+      </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:24">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -23247,7 +23712,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:24">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -23308,8 +23773,11 @@
       <c r="V18">
         <v>1380</v>
       </c>
+      <c r="X18">
+        <v>524.42578100000003</v>
+      </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:24">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -23370,8 +23838,11 @@
       <c r="V19">
         <v>13900</v>
       </c>
+      <c r="X19">
+        <v>632.83886700000005</v>
+      </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:24">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -23432,8 +23903,11 @@
       <c r="V20">
         <v>1480</v>
       </c>
+      <c r="X20">
+        <v>1063.3701169999999</v>
+      </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:24">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -23494,8 +23968,11 @@
       <c r="V21">
         <v>1604</v>
       </c>
+      <c r="X21">
+        <v>1096.1835940000001</v>
+      </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -23556,8 +24033,11 @@
       <c r="V22">
         <v>1058</v>
       </c>
+      <c r="X22">
+        <v>503.69726600000001</v>
+      </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -23618,8 +24098,11 @@
       <c r="V23">
         <v>1663</v>
       </c>
+      <c r="X23">
+        <v>510.13574199999999</v>
+      </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -23680,8 +24163,11 @@
       <c r="V24">
         <v>1486</v>
       </c>
+      <c r="X24">
+        <v>199.52246099999999</v>
+      </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -23742,8 +24228,11 @@
       <c r="V25">
         <v>2380</v>
       </c>
+      <c r="X25">
+        <v>253.570312</v>
+      </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:24">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -23804,8 +24293,11 @@
       <c r="V26">
         <v>8693</v>
       </c>
+      <c r="X26">
+        <v>39516.113280999998</v>
+      </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:24">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -23866,8 +24358,11 @@
       <c r="V27">
         <v>1825</v>
       </c>
+      <c r="X27">
+        <v>372.328125</v>
+      </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:24">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -23928,8 +24423,11 @@
       <c r="V28">
         <v>1792</v>
       </c>
+      <c r="X28">
+        <v>1126.993164</v>
+      </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -23990,13 +24488,16 @@
       <c r="V29">
         <v>1343</v>
       </c>
+      <c r="X29">
+        <v>208.92089799999999</v>
+      </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -24043,7 +24544,7 @@
         <v>0.12578616352201299</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -24090,7 +24591,7 @@
         <v>0.19569471624266099</v>
       </c>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:24">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -24137,7 +24638,7 @@
         <v>0.15060240963855401</v>
       </c>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:24">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -24184,7 +24685,7 @@
         <v>0.13495276653171401</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:24">
       <c r="A36" t="s">
         <v>30</v>
       </c>
@@ -24231,7 +24732,7 @@
         <v>0.136054421768707</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:24">
       <c r="A37" t="s">
         <v>31</v>
       </c>
@@ -24278,7 +24779,7 @@
         <v>0.20964360587002101</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:24">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -24325,7 +24826,7 @@
         <v>0.13440860215053799</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:24">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -24372,7 +24873,7 @@
         <v>0.23923444976076599</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:24">
       <c r="A40" t="s">
         <v>34</v>
       </c>
@@ -24419,7 +24920,7 @@
         <v>0.20833333333333301</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:24">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -24466,7 +24967,7 @@
         <v>0.19417475728155301</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:24">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -24513,7 +25014,7 @@
         <v>0.12755102040816299</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:24">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -24560,12 +25061,12 @@
         <v>8.6880973066898404E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:24">
       <c r="A45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:24">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -24629,8 +25130,11 @@
       <c r="U46">
         <v>110.47</v>
       </c>
+      <c r="X46">
+        <v>0.26600000000000001</v>
+      </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:24">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -24694,8 +25198,11 @@
       <c r="U47">
         <v>230.39</v>
       </c>
+      <c r="X47">
+        <v>0.378</v>
+      </c>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:24">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -24759,8 +25266,11 @@
       <c r="U48">
         <v>66.27</v>
       </c>
+      <c r="X48">
+        <v>0.17799999999999999</v>
+      </c>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:24">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -24824,8 +25334,11 @@
       <c r="U49">
         <v>93.41</v>
       </c>
+      <c r="X49">
+        <v>0.189</v>
+      </c>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:24">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -24889,8 +25402,11 @@
       <c r="U50">
         <v>184.25</v>
       </c>
+      <c r="X50">
+        <v>0.29599999999999999</v>
+      </c>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:24">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -24954,8 +25470,11 @@
       <c r="U51">
         <v>209.71</v>
       </c>
+      <c r="X51">
+        <v>0.46800000000000003</v>
+      </c>
     </row>
-    <row r="52" spans="1:21">
+    <row r="52" spans="1:24">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -25019,8 +25538,11 @@
       <c r="U52">
         <v>244.02</v>
       </c>
+      <c r="X52">
+        <v>0.184</v>
+      </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:24">
       <c r="A53" t="s">
         <v>33</v>
       </c>
@@ -25084,8 +25606,11 @@
       <c r="U53">
         <v>380.21</v>
       </c>
+      <c r="X53">
+        <v>0.46700000000000003</v>
+      </c>
     </row>
-    <row r="54" spans="1:21">
+    <row r="54" spans="1:24">
       <c r="A54" t="s">
         <v>34</v>
       </c>
@@ -25149,8 +25674,11 @@
       <c r="U54">
         <v>363.31</v>
       </c>
+      <c r="X54">
+        <v>25</v>
+      </c>
     </row>
-    <row r="55" spans="1:21">
+    <row r="55" spans="1:24">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -25214,8 +25742,11 @@
       <c r="U55">
         <v>247.69</v>
       </c>
+      <c r="X55">
+        <v>0.45100000000000001</v>
+      </c>
     </row>
-    <row r="56" spans="1:21">
+    <row r="56" spans="1:24">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -25279,8 +25810,11 @@
       <c r="U56">
         <v>684.52</v>
       </c>
+      <c r="X56">
+        <v>0.17599999999999999</v>
+      </c>
     </row>
-    <row r="57" spans="1:21">
+    <row r="57" spans="1:24">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -25343,6 +25877,9 @@
       </c>
       <c r="U57">
         <v>145.94</v>
+      </c>
+      <c r="X57">
+        <v>0.20100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -25358,7 +25895,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="9" width="12.796875" customWidth="1"/>
@@ -25368,8 +25905,8 @@
     <col min="18" max="18" width="11.296875" customWidth="1"/>
     <col min="19" max="19" width="10.8984375" customWidth="1"/>
     <col min="20" max="20" width="9.3984375" customWidth="1"/>
-    <col min="21" max="23" width="12.796875" customWidth="1"/>
-    <col min="24" max="24" width="15.19921875" customWidth="1"/>
+    <col min="21" max="22" width="12.796875" customWidth="1"/>
+    <col min="23" max="23" width="14.19921875" customWidth="1"/>
     <col min="25" max="25" width="15.296875" customWidth="1"/>
     <col min="26" max="26" width="16.59765625" customWidth="1"/>
     <col min="27" max="27" width="16" customWidth="1"/>
@@ -25377,7 +25914,7 @@
     <col min="29" max="29" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -25388,12 +25925,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:24">
       <c r="K2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -25460,8 +25997,14 @@
       <c r="V3" t="s">
         <v>25</v>
       </c>
+      <c r="W3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="X3" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -25525,8 +26068,14 @@
       <c r="U4">
         <v>0.10299999999999999</v>
       </c>
+      <c r="W4">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="X4">
+        <v>0.171043</v>
+      </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:24">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -25590,8 +26139,14 @@
       <c r="U5">
         <v>0.91500000000000004</v>
       </c>
+      <c r="W5">
+        <v>0.13880999999999999</v>
+      </c>
+      <c r="X5">
+        <v>0.31703999999999999</v>
+      </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -25655,8 +26210,14 @@
       <c r="U6">
         <v>0.111</v>
       </c>
+      <c r="W6">
+        <v>0.13868</v>
+      </c>
+      <c r="X6">
+        <v>0.17954999999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -25720,8 +26281,14 @@
       <c r="U7">
         <v>0.184</v>
       </c>
+      <c r="W7">
+        <v>0.13877</v>
+      </c>
+      <c r="X7">
+        <v>0.16584599999999999</v>
+      </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -25785,8 +26352,11 @@
       <c r="U8">
         <v>0.17699999999999999</v>
       </c>
+      <c r="X8">
+        <v>0.190941</v>
+      </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -25850,8 +26420,14 @@
       <c r="U9">
         <v>0.21</v>
       </c>
+      <c r="W9">
+        <v>0.14387</v>
+      </c>
+      <c r="X9">
+        <v>0.19268199999999999</v>
+      </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -25915,8 +26491,14 @@
       <c r="U10">
         <v>0.16300000000000001</v>
       </c>
+      <c r="W10">
+        <v>0.13553999999999999</v>
+      </c>
+      <c r="X10">
+        <v>0.156449</v>
+      </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -25980,8 +26562,14 @@
       <c r="U11">
         <v>0.183</v>
       </c>
+      <c r="W11">
+        <v>0.13649</v>
+      </c>
+      <c r="X11">
+        <v>0.19232199999999999</v>
+      </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -26045,8 +26633,14 @@
       <c r="U12">
         <v>0.222</v>
       </c>
+      <c r="W12">
+        <v>0.14011000000000001</v>
+      </c>
+      <c r="X12">
+        <v>0.245118</v>
+      </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -26110,8 +26704,14 @@
       <c r="U13">
         <v>0.17</v>
       </c>
+      <c r="W13">
+        <v>0.13849</v>
+      </c>
+      <c r="X13">
+        <v>0.18124699999999999</v>
+      </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -26175,8 +26775,14 @@
       <c r="U14">
         <v>0.154</v>
       </c>
+      <c r="W14">
+        <v>0.13735</v>
+      </c>
+      <c r="X14">
+        <v>0.179868</v>
+      </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -26240,8 +26846,11 @@
       <c r="U15">
         <v>0.12</v>
       </c>
+      <c r="X15">
+        <v>0.197049</v>
+      </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:24">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -26249,7 +26858,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:24">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -26310,8 +26919,11 @@
       <c r="V18">
         <v>1380</v>
       </c>
+      <c r="X18">
+        <v>524.42578100000003</v>
+      </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:24">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -26372,8 +26984,11 @@
       <c r="V19">
         <v>13900</v>
       </c>
+      <c r="X19">
+        <v>632.83886700000005</v>
+      </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:24">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -26434,8 +27049,11 @@
       <c r="V20">
         <v>1480</v>
       </c>
+      <c r="X20">
+        <v>1063.3701169999999</v>
+      </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:24">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -26496,8 +27114,11 @@
       <c r="V21">
         <v>1604</v>
       </c>
+      <c r="X21">
+        <v>1096.1835940000001</v>
+      </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -26558,8 +27179,11 @@
       <c r="V22">
         <v>1058</v>
       </c>
+      <c r="X22">
+        <v>503.69726600000001</v>
+      </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -26620,8 +27244,11 @@
       <c r="V23">
         <v>1663</v>
       </c>
+      <c r="X23">
+        <v>510.13574199999999</v>
+      </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -26682,8 +27309,11 @@
       <c r="V24">
         <v>1486</v>
       </c>
+      <c r="X24">
+        <v>199.52246099999999</v>
+      </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -26744,8 +27374,11 @@
       <c r="V25">
         <v>2380</v>
       </c>
+      <c r="X25">
+        <v>253.570312</v>
+      </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:24">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -26806,8 +27439,11 @@
       <c r="V26">
         <v>8693</v>
       </c>
+      <c r="X26">
+        <v>39516.113280999998</v>
+      </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:24">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -26868,8 +27504,11 @@
       <c r="V27">
         <v>1825</v>
       </c>
+      <c r="X27">
+        <v>372.328125</v>
+      </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:24">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -26930,8 +27569,11 @@
       <c r="V28">
         <v>1792</v>
       </c>
+      <c r="X28">
+        <v>1126.993164</v>
+      </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -26992,13 +27634,16 @@
       <c r="V29">
         <v>1343</v>
       </c>
+      <c r="X29">
+        <v>208.92089799999999</v>
+      </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -27045,7 +27690,7 @@
         <v>0.12578616352201299</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -27092,7 +27737,7 @@
         <v>0.19569471624266099</v>
       </c>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:24">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -27139,7 +27784,7 @@
         <v>0.15060240963855401</v>
       </c>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:24">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -27186,7 +27831,7 @@
         <v>0.13495276653171401</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:24">
       <c r="A36" t="s">
         <v>30</v>
       </c>
@@ -27233,7 +27878,7 @@
         <v>0.136054421768707</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:24">
       <c r="A37" t="s">
         <v>31</v>
       </c>
@@ -27280,7 +27925,7 @@
         <v>0.20964360587002101</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:24">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -27327,7 +27972,7 @@
         <v>0.13440860215053799</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:24">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -27374,7 +28019,7 @@
         <v>0.23923444976076599</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:24">
       <c r="A40" t="s">
         <v>34</v>
       </c>
@@ -27421,7 +28066,7 @@
         <v>0.20833333333333301</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:24">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -27468,7 +28113,7 @@
         <v>0.19417475728155301</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:24">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -27515,7 +28160,7 @@
         <v>0.12755102040816299</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:24">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -27562,12 +28207,12 @@
         <v>8.6880973066898404E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:24">
       <c r="A45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:24">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -27631,8 +28276,11 @@
       <c r="U46">
         <v>110.47</v>
       </c>
+      <c r="X46">
+        <v>0.26600000000000001</v>
+      </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:24">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -27696,8 +28344,11 @@
       <c r="U47">
         <v>230.39</v>
       </c>
+      <c r="X47">
+        <v>0.378</v>
+      </c>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:24">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -27761,8 +28412,11 @@
       <c r="U48">
         <v>66.27</v>
       </c>
+      <c r="X48">
+        <v>0.17799999999999999</v>
+      </c>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:24">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -27826,8 +28480,11 @@
       <c r="U49">
         <v>93.41</v>
       </c>
+      <c r="X49">
+        <v>0.189</v>
+      </c>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:24">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -27891,8 +28548,11 @@
       <c r="U50">
         <v>184.25</v>
       </c>
+      <c r="X50">
+        <v>0.29599999999999999</v>
+      </c>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:24">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -27956,8 +28616,11 @@
       <c r="U51">
         <v>209.71</v>
       </c>
+      <c r="X51">
+        <v>0.46800000000000003</v>
+      </c>
     </row>
-    <row r="52" spans="1:21">
+    <row r="52" spans="1:24">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -28021,8 +28684,11 @@
       <c r="U52">
         <v>244.02</v>
       </c>
+      <c r="X52">
+        <v>0.184</v>
+      </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:24">
       <c r="A53" t="s">
         <v>33</v>
       </c>
@@ -28086,8 +28752,11 @@
       <c r="U53">
         <v>380.21</v>
       </c>
+      <c r="X53">
+        <v>0.46700000000000003</v>
+      </c>
     </row>
-    <row r="54" spans="1:21">
+    <row r="54" spans="1:24">
       <c r="A54" t="s">
         <v>34</v>
       </c>
@@ -28151,8 +28820,11 @@
       <c r="U54">
         <v>363.31</v>
       </c>
+      <c r="X54">
+        <v>25</v>
+      </c>
     </row>
-    <row r="55" spans="1:21">
+    <row r="55" spans="1:24">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -28216,8 +28888,11 @@
       <c r="U55">
         <v>247.69</v>
       </c>
+      <c r="X55">
+        <v>0.45100000000000001</v>
+      </c>
     </row>
-    <row r="56" spans="1:21">
+    <row r="56" spans="1:24">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -28281,8 +28956,11 @@
       <c r="U56">
         <v>684.52</v>
       </c>
+      <c r="X56">
+        <v>0.17599999999999999</v>
+      </c>
     </row>
-    <row r="57" spans="1:21">
+    <row r="57" spans="1:24">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -28345,6 +29023,9 @@
       </c>
       <c r="U57">
         <v>145.94</v>
+      </c>
+      <c r="X57">
+        <v>0.20100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -28360,7 +29041,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="9" width="12.796875" customWidth="1"/>
@@ -28368,8 +29049,8 @@
     <col min="11" max="11" width="16" customWidth="1"/>
     <col min="12" max="17" width="12.796875" customWidth="1"/>
     <col min="18" max="18" width="17" customWidth="1"/>
-    <col min="19" max="23" width="12.796875" customWidth="1"/>
-    <col min="24" max="24" width="15.19921875" customWidth="1"/>
+    <col min="19" max="22" width="12.796875" customWidth="1"/>
+    <col min="23" max="23" width="14.19921875" customWidth="1"/>
     <col min="25" max="25" width="15.296875" customWidth="1"/>
     <col min="26" max="26" width="16.59765625" customWidth="1"/>
     <col min="27" max="27" width="16" customWidth="1"/>
@@ -28377,7 +29058,7 @@
     <col min="29" max="29" width="8.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -28388,12 +29069,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:24">
       <c r="K2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:24">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -28460,8 +29141,14 @@
       <c r="V3" t="s">
         <v>25</v>
       </c>
+      <c r="W3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="X3" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:24">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -28525,8 +29212,14 @@
       <c r="U4">
         <v>0.10299999999999999</v>
       </c>
+      <c r="W4">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="X4">
+        <v>0.171043</v>
+      </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:24">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -28590,8 +29283,14 @@
       <c r="U5">
         <v>0.91500000000000004</v>
       </c>
+      <c r="W5">
+        <v>0.13880999999999999</v>
+      </c>
+      <c r="X5">
+        <v>0.31703999999999999</v>
+      </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:24">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -28655,8 +29354,14 @@
       <c r="U6">
         <v>0.111</v>
       </c>
+      <c r="W6">
+        <v>0.13868</v>
+      </c>
+      <c r="X6">
+        <v>0.17954999999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:24">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -28720,8 +29425,14 @@
       <c r="U7">
         <v>0.184</v>
       </c>
+      <c r="W7">
+        <v>0.13877</v>
+      </c>
+      <c r="X7">
+        <v>0.16584599999999999</v>
+      </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:24">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -28785,8 +29496,11 @@
       <c r="U8">
         <v>0.17699999999999999</v>
       </c>
+      <c r="X8">
+        <v>0.190941</v>
+      </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:24">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -28850,8 +29564,14 @@
       <c r="U9">
         <v>0.21</v>
       </c>
+      <c r="W9">
+        <v>0.14387</v>
+      </c>
+      <c r="X9">
+        <v>0.19268199999999999</v>
+      </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:24">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -28915,8 +29635,14 @@
       <c r="U10">
         <v>0.16300000000000001</v>
       </c>
+      <c r="W10">
+        <v>0.13553999999999999</v>
+      </c>
+      <c r="X10">
+        <v>0.156449</v>
+      </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:24">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -28980,8 +29706,14 @@
       <c r="U11">
         <v>0.183</v>
       </c>
+      <c r="W11">
+        <v>0.13649</v>
+      </c>
+      <c r="X11">
+        <v>0.19232199999999999</v>
+      </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:24">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -29045,8 +29777,14 @@
       <c r="U12">
         <v>0.222</v>
       </c>
+      <c r="W12">
+        <v>0.14011000000000001</v>
+      </c>
+      <c r="X12">
+        <v>0.245118</v>
+      </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:24">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -29110,8 +29848,14 @@
       <c r="U13">
         <v>0.17</v>
       </c>
+      <c r="W13">
+        <v>0.13849</v>
+      </c>
+      <c r="X13">
+        <v>0.18124699999999999</v>
+      </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:24">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -29175,8 +29919,14 @@
       <c r="U14">
         <v>0.154</v>
       </c>
+      <c r="W14">
+        <v>0.13735</v>
+      </c>
+      <c r="X14">
+        <v>0.179868</v>
+      </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:24">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -29240,8 +29990,11 @@
       <c r="U15">
         <v>0.12</v>
       </c>
+      <c r="X15">
+        <v>0.197049</v>
+      </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:24">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -29249,7 +30002,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:24">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -29310,8 +30063,11 @@
       <c r="V18">
         <v>1380</v>
       </c>
+      <c r="X18">
+        <v>524.42578100000003</v>
+      </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:24">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -29372,8 +30128,11 @@
       <c r="V19">
         <v>13900</v>
       </c>
+      <c r="X19">
+        <v>632.83886700000005</v>
+      </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:24">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -29434,8 +30193,11 @@
       <c r="V20">
         <v>1480</v>
       </c>
+      <c r="X20">
+        <v>1063.3701169999999</v>
+      </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:24">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -29496,8 +30258,11 @@
       <c r="V21">
         <v>1604</v>
       </c>
+      <c r="X21">
+        <v>1096.1835940000001</v>
+      </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:24">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -29558,8 +30323,11 @@
       <c r="V22">
         <v>1058</v>
       </c>
+      <c r="X22">
+        <v>503.69726600000001</v>
+      </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:24">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -29620,8 +30388,11 @@
       <c r="V23">
         <v>1663</v>
       </c>
+      <c r="X23">
+        <v>510.13574199999999</v>
+      </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:24">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -29682,8 +30453,11 @@
       <c r="V24">
         <v>1486</v>
       </c>
+      <c r="X24">
+        <v>199.52246099999999</v>
+      </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:24">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -29744,8 +30518,11 @@
       <c r="V25">
         <v>2380</v>
       </c>
+      <c r="X25">
+        <v>253.570312</v>
+      </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:24">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -29806,8 +30583,11 @@
       <c r="V26">
         <v>8693</v>
       </c>
+      <c r="X26">
+        <v>39516.113280999998</v>
+      </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:24">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -29868,8 +30648,11 @@
       <c r="V27">
         <v>1825</v>
       </c>
+      <c r="X27">
+        <v>372.328125</v>
+      </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:24">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -29930,8 +30713,11 @@
       <c r="V28">
         <v>1792</v>
       </c>
+      <c r="X28">
+        <v>1126.993164</v>
+      </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:24">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -29992,13 +30778,16 @@
       <c r="V29">
         <v>1343</v>
       </c>
+      <c r="X29">
+        <v>208.92089799999999</v>
+      </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:24">
       <c r="A31" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:24">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -30045,7 +30834,7 @@
         <v>0.12578616352201299</v>
       </c>
     </row>
-    <row r="33" spans="1:21">
+    <row r="33" spans="1:24">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -30092,7 +30881,7 @@
         <v>0.19569471624266099</v>
       </c>
     </row>
-    <row r="34" spans="1:21">
+    <row r="34" spans="1:24">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -30139,7 +30928,7 @@
         <v>0.15060240963855401</v>
       </c>
     </row>
-    <row r="35" spans="1:21">
+    <row r="35" spans="1:24">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -30186,7 +30975,7 @@
         <v>0.13495276653171401</v>
       </c>
     </row>
-    <row r="36" spans="1:21">
+    <row r="36" spans="1:24">
       <c r="A36" t="s">
         <v>30</v>
       </c>
@@ -30233,7 +31022,7 @@
         <v>0.136054421768707</v>
       </c>
     </row>
-    <row r="37" spans="1:21">
+    <row r="37" spans="1:24">
       <c r="A37" t="s">
         <v>31</v>
       </c>
@@ -30280,7 +31069,7 @@
         <v>0.20964360587002101</v>
       </c>
     </row>
-    <row r="38" spans="1:21">
+    <row r="38" spans="1:24">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -30327,7 +31116,7 @@
         <v>0.13440860215053799</v>
       </c>
     </row>
-    <row r="39" spans="1:21">
+    <row r="39" spans="1:24">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -30374,7 +31163,7 @@
         <v>0.23923444976076599</v>
       </c>
     </row>
-    <row r="40" spans="1:21">
+    <row r="40" spans="1:24">
       <c r="A40" t="s">
         <v>34</v>
       </c>
@@ -30421,7 +31210,7 @@
         <v>0.20833333333333301</v>
       </c>
     </row>
-    <row r="41" spans="1:21">
+    <row r="41" spans="1:24">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -30468,7 +31257,7 @@
         <v>0.19417475728155301</v>
       </c>
     </row>
-    <row r="42" spans="1:21">
+    <row r="42" spans="1:24">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -30515,7 +31304,7 @@
         <v>0.12755102040816299</v>
       </c>
     </row>
-    <row r="43" spans="1:21">
+    <row r="43" spans="1:24">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -30562,12 +31351,12 @@
         <v>8.6880973066898404E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:21">
+    <row r="45" spans="1:24">
       <c r="A45" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="46" spans="1:21">
+    <row r="46" spans="1:24">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -30631,8 +31420,11 @@
       <c r="U46">
         <v>110.47</v>
       </c>
+      <c r="X46">
+        <v>0.26600000000000001</v>
+      </c>
     </row>
-    <row r="47" spans="1:21">
+    <row r="47" spans="1:24">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -30696,8 +31488,11 @@
       <c r="U47">
         <v>230.39</v>
       </c>
+      <c r="X47">
+        <v>0.378</v>
+      </c>
     </row>
-    <row r="48" spans="1:21">
+    <row r="48" spans="1:24">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -30761,8 +31556,11 @@
       <c r="U48">
         <v>66.27</v>
       </c>
+      <c r="X48">
+        <v>0.17799999999999999</v>
+      </c>
     </row>
-    <row r="49" spans="1:21">
+    <row r="49" spans="1:24">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -30826,8 +31624,11 @@
       <c r="U49">
         <v>93.41</v>
       </c>
+      <c r="X49">
+        <v>0.189</v>
+      </c>
     </row>
-    <row r="50" spans="1:21">
+    <row r="50" spans="1:24">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -30891,8 +31692,11 @@
       <c r="U50">
         <v>184.25</v>
       </c>
+      <c r="X50">
+        <v>0.29599999999999999</v>
+      </c>
     </row>
-    <row r="51" spans="1:21">
+    <row r="51" spans="1:24">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -30956,8 +31760,11 @@
       <c r="U51">
         <v>209.71</v>
       </c>
+      <c r="X51">
+        <v>0.46800000000000003</v>
+      </c>
     </row>
-    <row r="52" spans="1:21">
+    <row r="52" spans="1:24">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -31021,8 +31828,11 @@
       <c r="U52">
         <v>244.02</v>
       </c>
+      <c r="X52">
+        <v>0.184</v>
+      </c>
     </row>
-    <row r="53" spans="1:21">
+    <row r="53" spans="1:24">
       <c r="A53" t="s">
         <v>33</v>
       </c>
@@ -31086,8 +31896,11 @@
       <c r="U53">
         <v>380.21</v>
       </c>
+      <c r="X53">
+        <v>0.46700000000000003</v>
+      </c>
     </row>
-    <row r="54" spans="1:21">
+    <row r="54" spans="1:24">
       <c r="A54" t="s">
         <v>34</v>
       </c>
@@ -31151,8 +31964,11 @@
       <c r="U54">
         <v>363.31</v>
       </c>
+      <c r="X54">
+        <v>25</v>
+      </c>
     </row>
-    <row r="55" spans="1:21">
+    <row r="55" spans="1:24">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -31216,8 +32032,11 @@
       <c r="U55">
         <v>247.69</v>
       </c>
+      <c r="X55">
+        <v>0.45100000000000001</v>
+      </c>
     </row>
-    <row r="56" spans="1:21">
+    <row r="56" spans="1:24">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -31281,8 +32100,11 @@
       <c r="U56">
         <v>684.52</v>
       </c>
+      <c r="X56">
+        <v>0.17599999999999999</v>
+      </c>
     </row>
-    <row r="57" spans="1:21">
+    <row r="57" spans="1:24">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -31345,6 +32167,9 @@
       </c>
       <c r="U57">
         <v>145.94</v>
+      </c>
+      <c r="X57">
+        <v>0.20100000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -31359,7 +32184,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AE57"/>
+  <dimension ref="A1:AK57"/>
   <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="9" width="12.796875" customWidth="1"/>
@@ -31386,9 +32211,12 @@
     <col min="30" max="30" width="9.8984375" customWidth="1"/>
     <col min="31" max="31" width="9.69921875" customWidth="1"/>
     <col min="32" max="32" width="8.796875" customWidth="1"/>
+    <col min="33" max="33" width="17" customWidth="1"/>
+    <col min="34" max="34" width="12.59765625" customWidth="1"/>
+    <col min="36" max="36" width="12.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:37">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -31408,7 +32236,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:37">
       <c r="L2" t="s">
         <v>3</v>
       </c>
@@ -31424,8 +32252,11 @@
       <c r="Y2" t="s">
         <v>44</v>
       </c>
+      <c r="AH2" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:37">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -31507,8 +32338,23 @@
       <c r="AE3" t="s">
         <v>22</v>
       </c>
+      <c r="AG3" t="s">
+        <v>61</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>7</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>60</v>
+      </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:37">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -31587,8 +32433,23 @@
       <c r="AE4">
         <v>37.86</v>
       </c>
+      <c r="AG4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH4">
+        <v>0.30197600000000002</v>
+      </c>
+      <c r="AI4">
+        <v>0.36239900000000003</v>
+      </c>
+      <c r="AJ4">
+        <v>0.168013</v>
+      </c>
+      <c r="AK4">
+        <v>0.171043</v>
+      </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:37">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -31667,8 +32528,23 @@
       <c r="AE5">
         <v>12.89</v>
       </c>
+      <c r="AG5" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH5">
+        <v>1.114933</v>
+      </c>
+      <c r="AI5">
+        <v>1.862663</v>
+      </c>
+      <c r="AJ5">
+        <v>0.468358</v>
+      </c>
+      <c r="AK5">
+        <v>0.31703999999999999</v>
+      </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:37">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -31747,8 +32623,23 @@
       <c r="AE6">
         <v>26.95</v>
       </c>
+      <c r="AG6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH6">
+        <v>0.458679</v>
+      </c>
+      <c r="AI6">
+        <v>1.1434880000000001</v>
+      </c>
+      <c r="AJ6">
+        <v>0.194274</v>
+      </c>
+      <c r="AK6">
+        <v>0.17954999999999999</v>
+      </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:37">
       <c r="A7" t="s">
         <v>29</v>
       </c>
@@ -31827,8 +32718,23 @@
       <c r="AE7">
         <v>30.18</v>
       </c>
+      <c r="AG7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH7">
+        <v>0.49727700000000002</v>
+      </c>
+      <c r="AI7">
+        <v>1.292597</v>
+      </c>
+      <c r="AJ7">
+        <v>0.19742999999999999</v>
+      </c>
+      <c r="AK7">
+        <v>0.16584599999999999</v>
+      </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:37">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -31907,8 +32813,23 @@
       <c r="AE8">
         <v>37.74</v>
       </c>
+      <c r="AG8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH8">
+        <v>0.363174</v>
+      </c>
+      <c r="AI8">
+        <v>0.43487799999999999</v>
+      </c>
+      <c r="AJ8">
+        <v>0.29427900000000001</v>
+      </c>
+      <c r="AK8">
+        <v>0.190941</v>
+      </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:37">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -31987,8 +32908,23 @@
       <c r="AE9">
         <v>21.36</v>
       </c>
+      <c r="AG9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH9">
+        <v>0.313581</v>
+      </c>
+      <c r="AI9">
+        <v>1.0231840000000001</v>
+      </c>
+      <c r="AJ9">
+        <v>0.23905699999999999</v>
+      </c>
+      <c r="AK9">
+        <v>0.19268199999999999</v>
+      </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:37">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -32067,8 +33003,23 @@
       <c r="AE10">
         <v>23.95</v>
       </c>
+      <c r="AG10" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH10">
+        <v>0.37761299999999998</v>
+      </c>
+      <c r="AI10">
+        <v>0.51433200000000001</v>
+      </c>
+      <c r="AJ10">
+        <v>0.18240899999999999</v>
+      </c>
+      <c r="AK10">
+        <v>0.156449</v>
+      </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:37">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -32147,8 +33098,23 @@
       <c r="AE11">
         <v>30.24</v>
       </c>
+      <c r="AG11" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH11">
+        <v>0.30224800000000002</v>
+      </c>
+      <c r="AI11">
+        <v>0.51481699999999997</v>
+      </c>
+      <c r="AJ11">
+        <v>0.25740400000000002</v>
+      </c>
+      <c r="AK11">
+        <v>0.19232199999999999</v>
+      </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:37">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -32227,8 +33193,23 @@
       <c r="AE12">
         <v>14</v>
       </c>
+      <c r="AG12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH12">
+        <v>0.839835</v>
+      </c>
+      <c r="AI12">
+        <v>0.915161</v>
+      </c>
+      <c r="AJ12">
+        <v>0.194441</v>
+      </c>
+      <c r="AK12">
+        <v>0.245118</v>
+      </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:37">
       <c r="A13" t="s">
         <v>35</v>
       </c>
@@ -32307,8 +33288,23 @@
       <c r="AE13">
         <v>29.96</v>
       </c>
+      <c r="AG13" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH13">
+        <v>0.293904</v>
+      </c>
+      <c r="AI13">
+        <v>0.80602300000000004</v>
+      </c>
+      <c r="AJ13">
+        <v>0.23652999999999999</v>
+      </c>
+      <c r="AK13">
+        <v>0.18124699999999999</v>
+      </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:37">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -32387,8 +33383,23 @@
       <c r="AE14">
         <v>30.25</v>
       </c>
+      <c r="AG14" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH14">
+        <v>0.70822300000000005</v>
+      </c>
+      <c r="AI14">
+        <v>1.81484</v>
+      </c>
+      <c r="AJ14">
+        <v>0.19484099999999999</v>
+      </c>
+      <c r="AK14">
+        <v>0.179868</v>
+      </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:37">
       <c r="A15" t="s">
         <v>37</v>
       </c>
@@ -32467,8 +33478,23 @@
       <c r="AE15">
         <v>26.31</v>
       </c>
+      <c r="AG15" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH15">
+        <v>0.250637</v>
+      </c>
+      <c r="AI15">
+        <v>0.28578599999999998</v>
+      </c>
+      <c r="AJ15">
+        <v>0.20114499999999999</v>
+      </c>
+      <c r="AK15">
+        <v>0.197049</v>
+      </c>
     </row>
-    <row r="17" spans="1:31">
+    <row r="17" spans="1:37">
       <c r="A17" t="s">
         <v>38</v>
       </c>
@@ -32484,8 +33510,11 @@
       <c r="Y17" t="s">
         <v>52</v>
       </c>
+      <c r="AG17" t="s">
+        <v>59</v>
+      </c>
     </row>
-    <row r="18" spans="1:31">
+    <row r="18" spans="1:37">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -32561,8 +33590,23 @@
       <c r="AE18">
         <v>20.260000000000002</v>
       </c>
+      <c r="AG18" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH18">
+        <v>2021.8242190000001</v>
+      </c>
+      <c r="AI18">
+        <v>4806.890625</v>
+      </c>
+      <c r="AJ18">
+        <v>5459.6337890000004</v>
+      </c>
+      <c r="AK18">
+        <v>524.42578100000003</v>
+      </c>
     </row>
-    <row r="19" spans="1:31">
+    <row r="19" spans="1:37">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -32638,8 +33682,23 @@
       <c r="AE19">
         <v>165.74</v>
       </c>
+      <c r="AG19" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH19">
+        <v>2323.4570309999999</v>
+      </c>
+      <c r="AI19">
+        <v>4306.7382809999999</v>
+      </c>
+      <c r="AJ19">
+        <v>4642.3369140000004</v>
+      </c>
+      <c r="AK19">
+        <v>632.83886700000005</v>
+      </c>
     </row>
-    <row r="20" spans="1:31">
+    <row r="20" spans="1:37">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -32715,8 +33774,23 @@
       <c r="AE20">
         <v>24.47</v>
       </c>
+      <c r="AG20" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH20">
+        <v>2030.5664059999999</v>
+      </c>
+      <c r="AI20">
+        <v>4826.6367190000001</v>
+      </c>
+      <c r="AJ20">
+        <v>5462.3427730000003</v>
+      </c>
+      <c r="AK20">
+        <v>1063.3701169999999</v>
+      </c>
     </row>
-    <row r="21" spans="1:31">
+    <row r="21" spans="1:37">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -32792,8 +33866,23 @@
       <c r="AE21">
         <v>24.3</v>
       </c>
+      <c r="AG21" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH21">
+        <v>2222.4726559999999</v>
+      </c>
+      <c r="AI21">
+        <v>4818.28125</v>
+      </c>
+      <c r="AJ21">
+        <v>5469.4560549999997</v>
+      </c>
+      <c r="AK21">
+        <v>1096.1835940000001</v>
+      </c>
     </row>
-    <row r="22" spans="1:31">
+    <row r="22" spans="1:37">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -32869,8 +33958,23 @@
       <c r="AE22">
         <v>17.39</v>
       </c>
+      <c r="AG22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH22">
+        <v>2557.8359380000002</v>
+      </c>
+      <c r="AI22">
+        <v>4796.2617190000001</v>
+      </c>
+      <c r="AJ22">
+        <v>5444.9472660000001</v>
+      </c>
+      <c r="AK22">
+        <v>503.69726600000001</v>
+      </c>
     </row>
-    <row r="23" spans="1:31">
+    <row r="23" spans="1:37">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -32946,8 +34050,23 @@
       <c r="AE23">
         <v>56.3</v>
       </c>
+      <c r="AG23" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH23">
+        <v>2066.0351559999999</v>
+      </c>
+      <c r="AI23">
+        <v>4655.6015619999998</v>
+      </c>
+      <c r="AJ23">
+        <v>5273.9091799999997</v>
+      </c>
+      <c r="AK23">
+        <v>510.13574199999999</v>
+      </c>
     </row>
-    <row r="24" spans="1:31">
+    <row r="24" spans="1:37">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -33023,8 +34142,23 @@
       <c r="AE24">
         <v>32.6</v>
       </c>
+      <c r="AG24" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH24">
+        <v>2168.7265619999998</v>
+      </c>
+      <c r="AI24">
+        <v>4742.2773440000001</v>
+      </c>
+      <c r="AJ24">
+        <v>5386.3271480000003</v>
+      </c>
+      <c r="AK24">
+        <v>199.52246099999999</v>
+      </c>
     </row>
-    <row r="25" spans="1:31">
+    <row r="25" spans="1:37">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -33100,8 +34234,23 @@
       <c r="AE25">
         <v>32.24</v>
       </c>
+      <c r="AG25" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH25">
+        <v>1708.84375</v>
+      </c>
+      <c r="AI25">
+        <v>4483.0703119999998</v>
+      </c>
+      <c r="AJ25">
+        <v>5101.5859380000002</v>
+      </c>
+      <c r="AK25">
+        <v>253.570312</v>
+      </c>
     </row>
-    <row r="26" spans="1:31">
+    <row r="26" spans="1:37">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -33177,8 +34326,23 @@
       <c r="AE26">
         <v>505.9</v>
       </c>
+      <c r="AG26" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH26">
+        <v>1267.7070309999999</v>
+      </c>
+      <c r="AI26">
+        <v>4465.4101559999999</v>
+      </c>
+      <c r="AJ26">
+        <v>5071.1660160000001</v>
+      </c>
+      <c r="AK26">
+        <v>39516.113280999998</v>
+      </c>
     </row>
-    <row r="27" spans="1:31">
+    <row r="27" spans="1:37">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -33254,8 +34418,23 @@
       <c r="AE27">
         <v>50.74</v>
       </c>
+      <c r="AG27" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH27">
+        <v>2158.9101559999999</v>
+      </c>
+      <c r="AI27">
+        <v>4498.1210940000001</v>
+      </c>
+      <c r="AJ27">
+        <v>5095.0986329999996</v>
+      </c>
+      <c r="AK27">
+        <v>372.328125</v>
+      </c>
     </row>
-    <row r="28" spans="1:31">
+    <row r="28" spans="1:37">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -33331,8 +34510,23 @@
       <c r="AE28">
         <v>29.56</v>
       </c>
+      <c r="AG28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH28">
+        <v>1958.2773440000001</v>
+      </c>
+      <c r="AI28">
+        <v>4800.6601559999999</v>
+      </c>
+      <c r="AJ28">
+        <v>5458.1650390000004</v>
+      </c>
+      <c r="AK28">
+        <v>1126.993164</v>
+      </c>
     </row>
-    <row r="29" spans="1:31">
+    <row r="29" spans="1:37">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -33408,8 +34602,23 @@
       <c r="AE29">
         <v>16.96</v>
       </c>
+      <c r="AG29" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH29">
+        <v>1597.1953120000001</v>
+      </c>
+      <c r="AI29">
+        <v>4811.0625</v>
+      </c>
+      <c r="AJ29">
+        <v>5417.0048829999996</v>
+      </c>
+      <c r="AK29">
+        <v>208.92089799999999</v>
+      </c>
     </row>
-    <row r="31" spans="1:31">
+    <row r="31" spans="1:37">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -33419,8 +34628,11 @@
       <c r="Y31" t="s">
         <v>54</v>
       </c>
+      <c r="AG31" t="s">
+        <v>62</v>
+      </c>
     </row>
-    <row r="32" spans="1:31">
+    <row r="32" spans="1:37">
       <c r="A32" t="s">
         <v>26</v>
       </c>
@@ -33481,8 +34693,20 @@
       <c r="AC32">
         <v>7.95</v>
       </c>
+      <c r="AG32" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH32">
+        <v>0.52526899999999999</v>
+      </c>
+      <c r="AI32">
+        <v>0.25629200000000002</v>
+      </c>
+      <c r="AJ32">
+        <v>0.84289899999999995</v>
+      </c>
     </row>
-    <row r="33" spans="1:31">
+    <row r="33" spans="1:37">
       <c r="A33" t="s">
         <v>27</v>
       </c>
@@ -33543,8 +34767,20 @@
       <c r="AC33">
         <v>5.1100000000000003</v>
       </c>
+      <c r="AG33" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH33">
+        <v>0.50329900000000005</v>
+      </c>
+      <c r="AI33">
+        <v>0.24745700000000001</v>
+      </c>
+      <c r="AJ33">
+        <v>0.86837200000000003</v>
+      </c>
     </row>
-    <row r="34" spans="1:31">
+    <row r="34" spans="1:37">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -33605,8 +34841,20 @@
       <c r="AC34">
         <v>6.64</v>
       </c>
+      <c r="AG34" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH34">
+        <v>0.39064599999999999</v>
+      </c>
+      <c r="AI34">
+        <v>0.22734799999999999</v>
+      </c>
+      <c r="AJ34">
+        <v>0.92323699999999997</v>
+      </c>
     </row>
-    <row r="35" spans="1:31">
+    <row r="35" spans="1:37">
       <c r="A35" t="s">
         <v>29</v>
       </c>
@@ -33667,8 +34915,20 @@
       <c r="AC35">
         <v>7.41</v>
       </c>
+      <c r="AG35" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH35">
+        <v>0.39323999999999998</v>
+      </c>
+      <c r="AI35">
+        <v>0.224387</v>
+      </c>
+      <c r="AJ35">
+        <v>0.71404800000000002</v>
+      </c>
     </row>
-    <row r="36" spans="1:31">
+    <row r="36" spans="1:37">
       <c r="A36" t="s">
         <v>30</v>
       </c>
@@ -33729,8 +34989,20 @@
       <c r="AC36">
         <v>7.35</v>
       </c>
+      <c r="AG36" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH36">
+        <v>0.47320299999999998</v>
+      </c>
+      <c r="AI36">
+        <v>0.24828700000000001</v>
+      </c>
+      <c r="AJ36">
+        <v>0.80028500000000002</v>
+      </c>
     </row>
-    <row r="37" spans="1:31">
+    <row r="37" spans="1:37">
       <c r="A37" t="s">
         <v>31</v>
       </c>
@@ -33791,8 +35063,20 @@
       <c r="AC37">
         <v>4.7699999999999996</v>
       </c>
+      <c r="AG37" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH37">
+        <v>0.28071499999999999</v>
+      </c>
+      <c r="AI37">
+        <v>0.22880700000000001</v>
+      </c>
+      <c r="AJ37">
+        <v>0.62939699999999998</v>
+      </c>
     </row>
-    <row r="38" spans="1:31">
+    <row r="38" spans="1:37">
       <c r="A38" t="s">
         <v>32</v>
       </c>
@@ -33853,8 +35137,20 @@
       <c r="AC38">
         <v>7.44</v>
       </c>
+      <c r="AG38" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH38">
+        <v>0.28042800000000001</v>
+      </c>
+      <c r="AI38">
+        <v>0.235206</v>
+      </c>
+      <c r="AJ38">
+        <v>0.71379099999999995</v>
+      </c>
     </row>
-    <row r="39" spans="1:31">
+    <row r="39" spans="1:37">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -33915,8 +35211,20 @@
       <c r="AC39">
         <v>4.18</v>
       </c>
+      <c r="AG39" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH39">
+        <v>0.27169199999999999</v>
+      </c>
+      <c r="AI39">
+        <v>0.227655</v>
+      </c>
+      <c r="AJ39">
+        <v>0.63714400000000004</v>
+      </c>
     </row>
-    <row r="40" spans="1:31">
+    <row r="40" spans="1:37">
       <c r="A40" t="s">
         <v>34</v>
       </c>
@@ -33977,8 +35285,20 @@
       <c r="AC40">
         <v>4.8</v>
       </c>
+      <c r="AG40" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH40">
+        <v>0.25173400000000001</v>
+      </c>
+      <c r="AI40">
+        <v>0.213057</v>
+      </c>
+      <c r="AJ40">
+        <v>0.66978000000000004</v>
+      </c>
     </row>
-    <row r="41" spans="1:31">
+    <row r="41" spans="1:37">
       <c r="A41" t="s">
         <v>35</v>
       </c>
@@ -34039,8 +35359,20 @@
       <c r="AC41">
         <v>5.15</v>
       </c>
+      <c r="AG41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH41">
+        <v>0.29743799999999998</v>
+      </c>
+      <c r="AI41">
+        <v>0.230603</v>
+      </c>
+      <c r="AJ41">
+        <v>0.65063700000000002</v>
+      </c>
     </row>
-    <row r="42" spans="1:31">
+    <row r="42" spans="1:37">
       <c r="A42" t="s">
         <v>36</v>
       </c>
@@ -34101,8 +35433,20 @@
       <c r="AC42">
         <v>7.84</v>
       </c>
+      <c r="AG42" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH42">
+        <v>0.39188899999999999</v>
+      </c>
+      <c r="AI42">
+        <v>0.22411800000000001</v>
+      </c>
+      <c r="AJ42">
+        <v>0.77076699999999998</v>
+      </c>
     </row>
-    <row r="43" spans="1:31">
+    <row r="43" spans="1:37">
       <c r="A43" t="s">
         <v>37</v>
       </c>
@@ -34163,8 +35507,20 @@
       <c r="AC43">
         <v>11.51</v>
       </c>
+      <c r="AG43" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH43">
+        <v>0.37688500000000003</v>
+      </c>
+      <c r="AI43">
+        <v>0.25006699999999998</v>
+      </c>
+      <c r="AJ43">
+        <v>0.73384899999999997</v>
+      </c>
     </row>
-    <row r="45" spans="1:31">
+    <row r="45" spans="1:37">
       <c r="A45" t="s">
         <v>40</v>
       </c>
@@ -34174,8 +35530,11 @@
       <c r="Y45" t="s">
         <v>55</v>
       </c>
+      <c r="AG45" t="s">
+        <v>58</v>
+      </c>
     </row>
-    <row r="46" spans="1:31">
+    <row r="46" spans="1:37">
       <c r="A46" t="s">
         <v>26</v>
       </c>
@@ -34254,8 +35613,23 @@
       <c r="AE46">
         <v>2.2999999999999998</v>
       </c>
+      <c r="AG46" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH46">
+        <v>0.21</v>
+      </c>
+      <c r="AI46">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="AJ46">
+        <v>7.9000000000000001E-2</v>
+      </c>
+      <c r="AK46">
+        <v>0.26600000000000001</v>
+      </c>
     </row>
-    <row r="47" spans="1:31">
+    <row r="47" spans="1:37">
       <c r="A47" t="s">
         <v>27</v>
       </c>
@@ -34334,8 +35708,23 @@
       <c r="AE47">
         <v>21.27</v>
       </c>
+      <c r="AG47" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH47">
+        <v>0.192</v>
+      </c>
+      <c r="AI47">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="AJ47">
+        <v>7.6999999999999999E-2</v>
+      </c>
+      <c r="AK47">
+        <v>0.378</v>
+      </c>
     </row>
-    <row r="48" spans="1:31">
+    <row r="48" spans="1:37">
       <c r="A48" t="s">
         <v>28</v>
       </c>
@@ -34414,8 +35803,23 @@
       <c r="AE48">
         <v>5.12</v>
       </c>
+      <c r="AG48" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH48">
+        <v>0.189</v>
+      </c>
+      <c r="AI48">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="AJ48">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="AK48">
+        <v>0.17799999999999999</v>
+      </c>
     </row>
-    <row r="49" spans="1:31">
+    <row r="49" spans="1:37">
       <c r="A49" t="s">
         <v>29</v>
       </c>
@@ -34494,8 +35898,23 @@
       <c r="AE49">
         <v>6.07</v>
       </c>
+      <c r="AG49" t="s">
+        <v>29</v>
+      </c>
+      <c r="AH49">
+        <v>0.183</v>
+      </c>
+      <c r="AI49">
+        <v>0.05</v>
+      </c>
+      <c r="AJ49">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="AK49">
+        <v>0.189</v>
+      </c>
     </row>
-    <row r="50" spans="1:31">
+    <row r="50" spans="1:37">
       <c r="A50" t="s">
         <v>30</v>
       </c>
@@ -34574,8 +35993,23 @@
       <c r="AE50">
         <v>1.45</v>
       </c>
+      <c r="AG50" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH50">
+        <v>0.217</v>
+      </c>
+      <c r="AI50">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="AJ50">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="AK50">
+        <v>0.29599999999999999</v>
+      </c>
     </row>
-    <row r="51" spans="1:31">
+    <row r="51" spans="1:37">
       <c r="A51" t="s">
         <v>31</v>
       </c>
@@ -34654,8 +36088,23 @@
       <c r="AE51">
         <v>7.87</v>
       </c>
+      <c r="AG51" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH51">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="AI51">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="AJ51">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="AK51">
+        <v>0.46800000000000003</v>
+      </c>
     </row>
-    <row r="52" spans="1:31">
+    <row r="52" spans="1:37">
       <c r="A52" t="s">
         <v>32</v>
       </c>
@@ -34734,8 +36183,23 @@
       <c r="AE52">
         <v>2.97</v>
       </c>
+      <c r="AG52" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH52">
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="AI52">
+        <v>0.05</v>
+      </c>
+      <c r="AJ52">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="AK52">
+        <v>0.184</v>
+      </c>
     </row>
-    <row r="53" spans="1:31">
+    <row r="53" spans="1:37">
       <c r="A53" t="s">
         <v>33</v>
       </c>
@@ -34814,8 +36278,23 @@
       <c r="AE53">
         <v>4.2300000000000004</v>
       </c>
+      <c r="AG53" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH53">
+        <v>0.16</v>
+      </c>
+      <c r="AI53">
+        <v>0.05</v>
+      </c>
+      <c r="AJ53">
+        <v>0.06</v>
+      </c>
+      <c r="AK53">
+        <v>0.46700000000000003</v>
+      </c>
     </row>
-    <row r="54" spans="1:31">
+    <row r="54" spans="1:37">
       <c r="A54" t="s">
         <v>34</v>
       </c>
@@ -34894,8 +36373,23 @@
       <c r="AE54">
         <v>35.909999999999997</v>
       </c>
+      <c r="AG54" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH54">
+        <v>0.154</v>
+      </c>
+      <c r="AI54">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="AJ54">
+        <v>6.3E-2</v>
+      </c>
+      <c r="AK54">
+        <v>25</v>
+      </c>
     </row>
-    <row r="55" spans="1:31">
+    <row r="55" spans="1:37">
       <c r="A55" t="s">
         <v>35</v>
       </c>
@@ -34974,8 +36468,23 @@
       <c r="AE55">
         <v>5.17</v>
       </c>
+      <c r="AG55" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH55">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="AI55">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="AJ55">
+        <v>6.2E-2</v>
+      </c>
+      <c r="AK55">
+        <v>0.45100000000000001</v>
+      </c>
     </row>
-    <row r="56" spans="1:31">
+    <row r="56" spans="1:37">
       <c r="A56" t="s">
         <v>36</v>
       </c>
@@ -35054,8 +36563,23 @@
       <c r="AE56">
         <v>6.86</v>
       </c>
+      <c r="AG56" t="s">
+        <v>36</v>
+      </c>
+      <c r="AH56">
+        <v>0.184</v>
+      </c>
+      <c r="AI56">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="AJ56">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="AK56">
+        <v>0.17599999999999999</v>
+      </c>
     </row>
-    <row r="57" spans="1:31">
+    <row r="57" spans="1:37">
       <c r="A57" t="s">
         <v>37</v>
       </c>
@@ -35133,6 +36657,21 @@
       </c>
       <c r="AE57">
         <v>0.8</v>
+      </c>
+      <c r="AG57" t="s">
+        <v>37</v>
+      </c>
+      <c r="AH57">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="AI57">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="AJ57">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="AK57">
+        <v>0.20100000000000001</v>
       </c>
     </row>
   </sheetData>
